--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8503604D-00E3-44EC-A56E-36E5CE426C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90165507-EF03-4DD8-A8E4-9D120D259400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="составные" sheetId="3" r:id="rId1"/>
-    <sheet name="Составные_важные" sheetId="4" r:id="rId2"/>
+    <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
+    <sheet name="составные" sheetId="3" r:id="rId2"/>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId3"/>
     <sheet name="Неизменные" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>тема половых отношений была запретной</t>
   </si>
@@ -121,6 +121,135 @@
   </si>
   <si>
     <t>волшебного наследия</t>
+  </si>
+  <si>
+    <t>русской волшебной школы</t>
+  </si>
+  <si>
+    <t>русского волшебного учебного заведения</t>
+  </si>
+  <si>
+    <t>волшебной школы</t>
+  </si>
+  <si>
+    <t>волшебного учебного заведения</t>
+  </si>
+  <si>
+    <t>русской волшебной цивилизации</t>
+  </si>
+  <si>
+    <t>русского волшебного общества</t>
+  </si>
+  <si>
+    <t>русская волшебная цивилизация</t>
+  </si>
+  <si>
+    <t>русское волшебное общество</t>
+  </si>
+  <si>
+    <t>волшебной русской культуры</t>
+  </si>
+  <si>
+    <t>волшебного русского наследия</t>
+  </si>
+  <si>
+    <t>волшебная русская культура</t>
+  </si>
+  <si>
+    <t>волшебное русское наследие</t>
+  </si>
+  <si>
+    <t>волшебную русскую культуру</t>
+  </si>
+  <si>
+    <t>старой волшебной русской культуры</t>
+  </si>
+  <si>
+    <t>старого волшебного русского наследия</t>
+  </si>
+  <si>
+    <t>энергия чи связана</t>
+  </si>
+  <si>
+    <t>заряд чи связан</t>
+  </si>
+  <si>
+    <t>Энергия фи усваивалась и накапливалась</t>
+  </si>
+  <si>
+    <t>Заряд фи усваивался и накапливался</t>
+  </si>
+  <si>
+    <t>энергия ми образовывалась</t>
+  </si>
+  <si>
+    <t>заряд ми образовывался</t>
+  </si>
+  <si>
+    <t>Накопление в организме энергии</t>
+  </si>
+  <si>
+    <t>Накопление в живом теле зарядов</t>
+  </si>
+  <si>
+    <t>энергия ли рождалась</t>
+  </si>
+  <si>
+    <t>заряд ли рождался</t>
+  </si>
+  <si>
+    <t>христианская поза</t>
+  </si>
+  <si>
+    <t>церковное положение</t>
+  </si>
+  <si>
+    <t>христианскую позу</t>
+  </si>
+  <si>
+    <t>христианской позой</t>
+  </si>
+  <si>
+    <t>церковным положением</t>
+  </si>
+  <si>
+    <t>действием энергии эмоций, которая называлась</t>
+  </si>
+  <si>
+    <t>действием заряда чувств, который назывался</t>
+  </si>
+  <si>
+    <t>русскую культуру</t>
+  </si>
+  <si>
+    <t>русское наследие</t>
+  </si>
+  <si>
+    <t>русская культура</t>
+  </si>
+  <si>
+    <t>русской культурой</t>
+  </si>
+  <si>
+    <t>русским наследием</t>
+  </si>
+  <si>
+    <t xml:space="preserve">погибшей высокоразвитой цивилизации, владевшей </t>
+  </si>
+  <si>
+    <t xml:space="preserve">погибшего высокоразвитого общества, владевшим </t>
+  </si>
+  <si>
+    <t>погибшей высокоразвитой цивилизации</t>
+  </si>
+  <si>
+    <t>погибшего высокоразвитого общества</t>
+  </si>
+  <si>
+    <t xml:space="preserve">была понятна совершенно иная форма </t>
+  </si>
+  <si>
+    <t>был понятен совершенно иной про-образ</t>
   </si>
 </sst>
 </file>
@@ -437,8 +566,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="61.26953125" customWidth="1"/>
+    <col min="2" max="2" width="47.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33B77-A4FE-48AE-9A13-FA7A259937FD}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.7265625" customWidth="1"/>
@@ -493,66 +756,60 @@
         <v>29</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="61.26953125" customWidth="1"/>
-    <col min="2" max="2" width="47.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -562,10 +819,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="60.26953125" customWidth="1"/>
     <col min="2" max="2" width="53.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -591,6 +848,62 @@
       </c>
       <c r="B3" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90165507-EF03-4DD8-A8E4-9D120D259400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44346C5E-B259-4825-9BA7-916BE26E2759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44346C5E-B259-4825-9BA7-916BE26E2759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033CDAEC-2B59-4E1A-9CB0-DE2C1824BF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
   <si>
     <t>тема половых отношений была запретной</t>
   </si>
@@ -250,6 +250,24 @@
   </si>
   <si>
     <t>был понятен совершенно иной про-образ</t>
+  </si>
+  <si>
+    <t>Непереворачиваемой эта поза</t>
+  </si>
+  <si>
+    <t>Непереворачиваемым это положение</t>
+  </si>
+  <si>
+    <t>долго совершать половой акт, он</t>
+  </si>
+  <si>
+    <t>долго совершать половое действие, оно</t>
+  </si>
+  <si>
+    <t>пара наполняется энергией, которая</t>
+  </si>
+  <si>
+    <t>двойка наполняется за-рядом, который</t>
   </si>
 </sst>
 </file>
@@ -567,14 +585,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="61.26953125" customWidth="1"/>
-    <col min="2" max="2" width="47.90625" customWidth="1"/>
+    <col min="1" max="1" width="61.28515625" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -582,7 +600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -590,7 +608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -598,7 +616,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -606,7 +624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -614,7 +632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -622,7 +640,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -630,7 +648,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -638,7 +656,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -646,7 +664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -654,7 +672,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -662,7 +680,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -670,7 +688,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -678,7 +696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -686,12 +704,20 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>71</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -702,13 +728,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33B77-A4FE-48AE-9A13-FA7A259937FD}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7265625" customWidth="1"/>
-    <col min="2" max="2" width="54.54296875" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" customWidth="1"/>
+    <col min="2" max="2" width="54.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -716,7 +742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -724,7 +750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -732,7 +758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -740,7 +766,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -748,7 +774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -756,7 +782,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -764,7 +790,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -772,7 +798,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -780,7 +806,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -788,7 +814,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -796,7 +822,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -804,7 +830,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -819,14 +845,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.26953125" customWidth="1"/>
-    <col min="2" max="2" width="53.36328125" customWidth="1"/>
+    <col min="1" max="1" width="60.28515625" customWidth="1"/>
+    <col min="2" max="2" width="53.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -834,7 +860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -842,7 +868,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -850,7 +876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -858,7 +884,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -866,7 +892,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -874,7 +900,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -882,7 +908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -890,7 +916,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -898,12 +924,28 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -914,13 +956,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AFEECF-5CA4-4A3D-9836-5735AC26D3E6}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
-    <col min="2" max="2" width="45.36328125" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033CDAEC-2B59-4E1A-9CB0-DE2C1824BF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160960A6-1179-453B-A0E5-A6943D54907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>тема половых отношений была запретной</t>
   </si>
@@ -268,19 +268,38 @@
   </si>
   <si>
     <t>двойка наполняется за-рядом, который</t>
+  </si>
+  <si>
+    <t>был половой акт, длящийся</t>
+  </si>
+  <si>
+    <t>было половое действие, длящееся</t>
+  </si>
+  <si>
+    <t>Простая традиция, но она сохраняла</t>
+  </si>
+  <si>
+    <t>Простой устой, но он сохранял</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -303,8 +322,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -586,13 +606,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="61.28515625" customWidth="1"/>
-    <col min="2" max="2" width="47.85546875" customWidth="1"/>
+    <col min="1" max="1" width="61.26953125" customWidth="1"/>
+    <col min="2" max="2" width="47.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -600,7 +620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -608,7 +628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -616,7 +636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -624,7 +644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -632,7 +652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -640,7 +660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -648,7 +668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -656,7 +676,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -664,7 +684,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -672,7 +692,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -680,7 +700,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -688,7 +708,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -696,7 +716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -704,7 +724,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -712,7 +732,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -728,13 +748,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED33B77-A4FE-48AE-9A13-FA7A259937FD}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
-    <col min="2" max="2" width="54.5703125" customWidth="1"/>
+    <col min="1" max="1" width="39.7265625" customWidth="1"/>
+    <col min="2" max="2" width="54.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -742,7 +762,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -750,7 +770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -758,7 +778,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -766,7 +786,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -774,7 +794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -782,7 +802,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -790,7 +810,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -798,7 +818,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -806,7 +826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -814,7 +834,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -822,7 +842,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -830,7 +850,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -845,14 +865,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="60.28515625" customWidth="1"/>
-    <col min="2" max="2" width="53.42578125" customWidth="1"/>
+    <col min="1" max="1" width="60.26953125" customWidth="1"/>
+    <col min="2" max="2" width="53.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -860,7 +880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -868,7 +888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -876,7 +896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -884,7 +904,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -892,7 +912,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -900,7 +920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -908,7 +928,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -916,7 +936,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -924,7 +944,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -932,7 +952,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -940,12 +960,28 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>77</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -956,13 +992,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AFEECF-5CA4-4A3D-9836-5735AC26D3E6}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="45.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160960A6-1179-453B-A0E5-A6943D54907D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7492C236-5F9D-4E91-9E61-E0209F168D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
     <sheet name="составные" sheetId="3" r:id="rId2"/>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId3"/>
     <sheet name="Неизменные" sheetId="2" r:id="rId4"/>
+    <sheet name="Неизменные_длинные" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
   <si>
     <t>тема половых отношений была запретной</t>
   </si>
@@ -280,6 +281,48 @@
   </si>
   <si>
     <t>Простой устой, но он сохранял</t>
+  </si>
+  <si>
+    <t>католическая традиция, специально внедрённая</t>
+  </si>
+  <si>
+    <t>католический устой, целенаправленно внедрённый</t>
+  </si>
+  <si>
+    <t>устойчивую родовую группу</t>
+  </si>
+  <si>
+    <t>устойчивое родовое подразделение</t>
+  </si>
+  <si>
+    <t>такие пары подлежали ликвидации</t>
+  </si>
+  <si>
+    <t>такие возлюбленные подлежали уничтожению</t>
+  </si>
+  <si>
+    <t>Такой паре обезьяньи</t>
+  </si>
+  <si>
+    <t>Таким мужчине и женщине обезьяньи</t>
+  </si>
+  <si>
+    <t>формирует эталон женщины, который</t>
+  </si>
+  <si>
+    <t>создаёт образец женщины, которая</t>
+  </si>
+  <si>
+    <t>него нет пары</t>
+  </si>
+  <si>
+    <t>него нет женщины</t>
+  </si>
+  <si>
+    <t>Какую гармонию можно найти вне себя, если внутри она у вас уже будет изуродована</t>
+  </si>
+  <si>
+    <t>Какое равно-весие можно найти вне себя, если внутри оно у вас уже будет изуродовано</t>
   </si>
 </sst>
 </file>
@@ -605,11 +648,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.26953125" customWidth="1"/>
-    <col min="2" max="2" width="47.81640625" customWidth="1"/>
+    <col min="2" max="2" width="56.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -738,6 +781,46 @@
       </c>
       <c r="B16" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -865,7 +948,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60.26953125" customWidth="1"/>
@@ -982,6 +1065,14 @@
       </c>
       <c r="B14" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1009,4 +1100,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9C7E18-A466-479A-89BD-4F20E2AD6654}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="84" customWidth="1"/>
+    <col min="2" max="2" width="72.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7492C236-5F9D-4E91-9E61-E0209F168D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F08A84-7130-4C9D-AF7D-D0E90F141DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="107">
   <si>
     <t>тема половых отношений была запретной</t>
   </si>
@@ -323,6 +323,36 @@
   </si>
   <si>
     <t>Какое равно-весие можно найти вне себя, если внутри оно у вас уже будет изуродовано</t>
+  </si>
+  <si>
+    <t>какая эмоция при этом у него возникала и чем она</t>
+  </si>
+  <si>
+    <t>какое чувство при этом у него возникало и чем оно</t>
+  </si>
+  <si>
+    <t>ушло из современной культуры, поскольку в неё</t>
+  </si>
+  <si>
+    <t>ушло из современного наследия, поскольку в него</t>
+  </si>
+  <si>
+    <t>в нашей древлеправославной культуре</t>
+  </si>
+  <si>
+    <t>в нашем древлеправославном наследиии</t>
+  </si>
+  <si>
+    <t>нашей древлеправославной культуре</t>
+  </si>
+  <si>
+    <t>нашем древлеправославном наследиии</t>
+  </si>
+  <si>
+    <t>Высшая форма любви характерна</t>
+  </si>
+  <si>
+    <t>Высший образ любви присущ</t>
   </si>
 </sst>
 </file>
@@ -648,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B678DDF-91A9-48E8-BE0F-0D4541025386}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="61.26953125" customWidth="1"/>
@@ -821,6 +851,14 @@
       </c>
       <c r="B21" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="60.26953125" customWidth="1"/>
@@ -1075,6 +1113,30 @@
         <v>84</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1082,10 +1144,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2AFEECF-5CA4-4A3D-9836-5735AC26D3E6}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="1" max="1" width="51.36328125" customWidth="1"/>
     <col min="2" max="2" width="45.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1095,6 +1157,14 @@
       </c>
       <c r="B1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/словари/шемчук.xlsx
+++ b/словари/шемчук.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F08A84-7130-4C9D-AF7D-D0E90F141DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED935823-EF93-4104-8B63-5EA440EE3A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
